--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92535626033</v>
+        <v>46157.9310909843</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9310909843</v>
+        <v>46157.93365014085</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93365014085</v>
+        <v>46157.93666407215</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93666407215</v>
+        <v>46158.28191601977</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28191601977</v>
+        <v>46158.29711349576</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29711349576</v>
+        <v>46158.29786542591</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29786542591</v>
+        <v>46158.33352529611</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33352529611</v>
+        <v>46158.37209040991</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37209040991</v>
+        <v>46158.37425882628</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
